--- a/fixtures/sml/pivot/basic.xlsx
+++ b/fixtures/sml/pivot/basic.xlsx
@@ -11,16 +11,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
+    <t>Sales</t>
+  </si>
+  <si>
     <t>South</t>
   </si>
   <si>
-    <t>Region</t>
+    <t>North</t>
   </si>
   <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>North</t>
+    <t>Region</t>
   </si>
 </sst>
 </file>
@@ -69,15 +69,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -85,7 +85,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>200</v>
@@ -93,7 +93,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>150</v>
